--- a/data/analysis/patent_aggregates.xlsx
+++ b/data/analysis/patent_aggregates.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Candidate 24_AHMED_NAEEM has a total of 10 patents listed. All of these patents are verifiable and international in scope. The candidate has not been listed as a sole, lead, or co-inventor on any of these patents, but has been credited as an unknown inventor role on all of them.</t>
+          <t>Candidate Ahmed Naeem holds 10 patent(s). 10 international patent(s). Overall applied innovation and IP profile is assessed as Strong.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>The candidate has a total of 1 patent listed in their record. This patent is from Pakistan and is verifiable. The candidate's role in the patent is unknown.</t>
+          <t>Candidate Muhammad Farrukh Qureshi holds 1 patent(s). 1 national (Pakistani) patent(s). Overall applied innovation and IP profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Candidate 01_MUHAMMAD_SALMAN has no patents listed in their CV.</t>
+          <t>Candidate MUHAMMAD SALMAN has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Candidate 02_MUHAMMAD_SHAHWAZ has no patents listed in their CV.</t>
+          <t>Candidate MUHAMMAD SHAHWAZ has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Candidate 03_NASIR_ALI_SHAH has no patents listed in their CV.</t>
+          <t>Candidate Nasir Ali Shah has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Candidate 05_MUHAMMAD_MAJID has no patents listed in their CV.</t>
+          <t>Candidate MUHAMMAD MAJID has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Candidate 06_FARMAN_ALI has no patents listed in their CV.</t>
+          <t>Candidate Farman Ali has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Candidate 07_FIZA_MURTAZA has no patents listed in their CV.</t>
+          <t>Candidate Fiza Murtaza has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Candidate 08_TAYYABA_GULL has no patents listed in their CV.</t>
+          <t>Candidate Tayyaba Gull has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Candidate 09_MUHAMMAD_ABUBAKAR has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Abubakar has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Candidate 10_MUHAMMAD_EHATISHAM has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Ehatisham has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Candidate 11_WAQAS_AMIN has no patents listed in their CV.</t>
+          <t>Candidate Waqas Amin has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Candidate 12_SYED_TAMOORULHASSAN has no patents listed in their CV.</t>
+          <t>Candidate SYED TAMOORULHASSAN has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Candidate 13_MANZOOR_ELLAHI has no patents listed in their CV.</t>
+          <t>Candidate Manzoor Ellahi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Candidate 14_SAROSH_TAHIR has no patents listed in their CV.</t>
+          <t>Candidate Sarosh Tahir has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Candidate 15_M_USMAN_ABBASI has no patents listed in their CV.</t>
+          <t>Candidate M. Usman Abbasi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Candidate 16_MUZZAMIL_GHAFFAR has no patents listed in their CV.</t>
+          <t>Candidate Muzzamil Ghaffar has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Candidate 17_SUHAIL_ASGHAR has no patents listed in their CV.</t>
+          <t>Candidate Suhail Asghar Qureshi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Candidate 18_MUHAMMAD_AMJAD has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Amjad has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Candidate 19_ASIM_MASOOD has no patents listed in their CV.</t>
+          <t>Candidate Asim Masood has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Candidate 20_SYED_FASIH_ALI has no patents listed in their CV.</t>
+          <t>Candidate Syed Fasih Ali has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Candidate 21_SAMAN_FATIMA has no patents listed in their CV.</t>
+          <t>Candidate Saman Fatima has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Candidate 22_ZEESHAN has no patents listed in their CV.</t>
+          <t>Candidate Zeeshan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Candidate 23_WAQAS_TARIQ_TOOR has no patents listed in their CV.</t>
+          <t>Candidate Waqas Tariq Toor has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Candidate 25_MUHAMMAD_ADEEL_ALTAF has no patents listed in their CV.</t>
+          <t>Candidate MUHAMMAD ADEEL ALTAF has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Candidate 26_AAMINA_AKBAR has no patents listed in their CV.</t>
+          <t>Candidate Aamina Akbar has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Candidate 27_SHAHEER has no patents listed in their CV.</t>
+          <t>Candidate Shaheer has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Candidate 28_IDRIS_KHAN has no patents listed in their CV.</t>
+          <t>Candidate Idris Khan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Candidate 29_MUHAMMAD_SARMAD_TARIQ has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Sarmad Tariq has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Candidate 30_FAHD_SIKANDAR_KHAN has no patents listed in their CV.</t>
+          <t>Candidate Fahd Sikandar Khan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Candidate 31_USMAN_MASUD has no patents listed in their CV.</t>
+          <t>Candidate Usman Masud has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Candidate 32_QAISAR_HUSSAIN_ALVI has no patents listed in their CV.</t>
+          <t>Candidate Qaisar Hussain Alvi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Candidate 33_QAMAR_ABBAS has no patents listed in their CV.</t>
+          <t>Candidate Qamar Abbas has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Candidate 34_SHAHZAD has no patents listed in their CV.</t>
+          <t>Candidate Shahzad has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Candidate 35_MATIULLAH_AHSAN has no patents listed in their CV.</t>
+          <t>Candidate Matiullah Ahsan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Candidate 36_SAMANA_BATOOL has no patents listed in their CV.</t>
+          <t>Candidate Samana Batool has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Candidate 37_SANIA_GUL has no patents listed in their CV.</t>
+          <t>Candidate Sania Gul has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Candidate 38_MUHAMMAD_MUSADIQ has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Musadiq Ahmed has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Candidate 39_MUHAMMAD_SAQIB has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Saqib has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Candidate 40_ABDUR_REHMAN has no patents listed in their CV.</t>
+          <t>Candidate Abdur Rehman has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Candidate 41_MUHAMMAD_AQEEL has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Aqeel has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Candidate 42_SAQIB_JAMIL has no patents listed in their CV.</t>
+          <t>Candidate Saqib Jamil has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Candidate 43_AMMARA_NASIM has no patents listed in their CV.</t>
+          <t>Candidate Ammara Nasim has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">

--- a/data/analysis/patent_aggregates.xlsx
+++ b/data/analysis/patent_aggregates.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,12 +1114,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>Sana Fatima Rizvi</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Ehatisham has no patents listed in their CV.</t>
+          <t>Candidate Sana Fatima Rizvi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1174,12 +1174,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11_WAQAS_AMIN</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Waqas Amin</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Candidate Waqas Amin has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Ehatisham has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>11_WAQAS_AMIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SYED TAMOORULHASSAN</t>
+          <t>Waqas Amin</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Candidate SYED TAMOORULHASSAN has no patents listed in their CV.</t>
+          <t>Candidate Waqas Amin has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1294,12 +1294,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13_MANZOOR_ELLAHI</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manzoor Ellahi</t>
+          <t>SYED TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Candidate Manzoor Ellahi has no patents listed in their CV.</t>
+          <t>Candidate SYED TAMOORULHASSAN has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>13_MANZOOR_ELLAHI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sarosh Tahir</t>
+          <t>Manzoor Ellahi</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Candidate Sarosh Tahir has no patents listed in their CV.</t>
+          <t>Candidate Manzoor Ellahi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M. Usman Abbasi</t>
+          <t>Sarosh Tahir</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Candidate M. Usman Abbasi has no patents listed in their CV.</t>
+          <t>Candidate Sarosh Tahir has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>M. Usman Abbasi</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Candidate Muzzamil Ghaffar has no patents listed in their CV.</t>
+          <t>Candidate M. Usman Abbasi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suhail Asghar Qureshi</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Candidate Suhail Asghar Qureshi has no patents listed in their CV.</t>
+          <t>Candidate Muzzamil Ghaffar has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Muhammad Amjad</t>
+          <t>Suhail Asghar Qureshi</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Amjad has no patents listed in their CV.</t>
+          <t>Candidate Suhail Asghar Qureshi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Asim Masood</t>
+          <t>Muhammad Amjad</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Candidate Asim Masood has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Amjad has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Syed Fasih Ali</t>
+          <t>Asim Masood</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Candidate Syed Fasih Ali has no patents listed in their CV.</t>
+          <t>Candidate Asim Masood has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saman Fatima</t>
+          <t>Syed Fasih Ali</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Candidate Saman Fatima has no patents listed in their CV.</t>
+          <t>Candidate Syed Fasih Ali has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1834,12 +1834,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeeshan</t>
+          <t>Saman Fatima</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Candidate Zeeshan has no patents listed in their CV.</t>
+          <t>Candidate Saman Fatima has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1894,12 +1894,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Waqas Tariq Toor</t>
+          <t>Zeeshan</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Candidate Waqas Tariq Toor has no patents listed in their CV.</t>
+          <t>Candidate Zeeshan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Waqas Tariq Toor</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Candidate MUHAMMAD ADEEL ALTAF has no patents listed in their CV.</t>
+          <t>Candidate Waqas Tariq Toor has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aamina Akbar</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Candidate Aamina Akbar has no patents listed in their CV.</t>
+          <t>Candidate MUHAMMAD ADEEL ALTAF has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2074,12 +2074,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>Aamina Akbar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Candidate Shaheer has no patents listed in their CV.</t>
+          <t>Candidate Aamina Akbar has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Idris Khan</t>
+          <t>Shaheer</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Candidate Idris Khan has no patents listed in their CV.</t>
+          <t>Candidate Shaheer has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2194,12 +2194,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Muhammad Sarmad Tariq</t>
+          <t>Idris Khan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Sarmad Tariq has no patents listed in their CV.</t>
+          <t>Candidate Idris Khan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2254,12 +2254,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan</t>
+          <t>Muhammad Sarmad Tariq</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Candidate Fahd Sikandar Khan has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Sarmad Tariq has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2314,12 +2314,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Usman Masud</t>
+          <t>Fahd Sikandar Khan</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Candidate Usman Masud has no patents listed in their CV.</t>
+          <t>Candidate Fahd Sikandar Khan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi</t>
+          <t>Usman Masud</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Candidate Qaisar Hussain Alvi has no patents listed in their CV.</t>
+          <t>Candidate Usman Masud has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2434,12 +2434,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qamar Abbas</t>
+          <t>Qaisar Hussain Alvi</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Candidate Qamar Abbas has no patents listed in their CV.</t>
+          <t>Candidate Qaisar Hussain Alvi has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2494,12 +2494,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shahzad</t>
+          <t>Qamar Abbas</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Candidate Shahzad has no patents listed in their CV.</t>
+          <t>Candidate Qamar Abbas has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2554,12 +2554,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matiullah Ahsan</t>
+          <t>Shahzad</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Candidate Matiullah Ahsan has no patents listed in their CV.</t>
+          <t>Candidate Shahzad has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2614,12 +2614,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samana Batool</t>
+          <t>Matiullah Ahsan</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Candidate Samana Batool has no patents listed in their CV.</t>
+          <t>Candidate Matiullah Ahsan has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -2674,12 +2674,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37_SANIA_GUL</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sania Gul</t>
+          <t>Samana Batool</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Candidate Sania Gul has no patents listed in their CV.</t>
+          <t>Candidate Samana Batool has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -2734,12 +2734,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>37_SANIA_GUL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq Ahmed</t>
+          <t>Sania Gul</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Musadiq Ahmed has no patents listed in their CV.</t>
+          <t>Candidate Sania Gul has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -2794,12 +2794,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Muhammad Saqib</t>
+          <t>Muhammad Musadiq Ahmed</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Saqib has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Musadiq Ahmed has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abdur Rehman</t>
+          <t>Muhammad Saqib</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Candidate Abdur Rehman has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Saqib has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -2914,12 +2914,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>Abdur Rehman</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Aqeel has no patents listed in their CV.</t>
+          <t>Candidate Abdur Rehman has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -2974,12 +2974,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Candidate Saqib Jamil has no patents listed in their CV.</t>
+          <t>Candidate Muhammad Aqeel has no patents listed in their CV.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3034,58 +3034,178 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>42_SAQIB_JAMIL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Saqib Jamil</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No Patents Listed</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Candidate Saqib Jamil has no patents listed in their CV.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>No Patents Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>43_AMMARA_NASIM</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Ammara Nasim</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>No Patents Listed</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No Patents Listed</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>Candidate Ammara Nasim has no patents listed in their CV.</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>No Patents Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No Patents Listed</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Candidate nan has no patents listed in their CV.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>No Patents Listed</t>
         </is>
